--- a/Flutter/Resoluciones de Pantalla.xlsx
+++ b/Flutter/Resoluciones de Pantalla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Chris ChaV\Dart\Flutter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DB64BB-400E-4B28-84CF-C54905A33AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9898091-B914-4226-826C-9E7821E319B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{0007F88B-D06F-4288-A870-FB5FE403ACEA}"/>
   </bookViews>
